--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269674.0748354853</v>
+        <v>274032.6002263779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>199813.870904442</v>
+        <v>202725.1043722281</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131100</v>
+        <v>78710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243702.2835004225</v>
+        <v>250857.9572858929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7209.05 - 3264724.22</t>
+          <t>11392.76 - 3903597.53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55416.1676321759</v>
+        <v>53818.21931361489</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>724404.1413457906</v>
+        <v>725796.6869795643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5338.153781152152</v>
+        <v>5369.490147978822</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4044.179742848622</v>
+        <v>4031.69778260121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2980</v>
+        <v>2780</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4536.621968380849</v>
+        <v>4576.837350585626</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150.58 - 66772.58</t>
+          <t>216.12 - 64489.91</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1192.119106306315</v>
+        <v>1220.758884307827</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13941.30053811154</v>
+        <v>13857.29890177667</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.03857048194227</v>
+        <v>37.38418756549958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.25870701510173</v>
+        <v>21.98114999057544</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50.22956503478908</v>
+        <v>50.44732695158963</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.44 - 766.99</t>
+          <t>0.42 - 1378.20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.905691973302372</v>
+        <v>3.768040465656767</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>122.1221608205125</v>
+        <v>120.3980130123977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.52249520213078e+64</v>
+        <v>2.280100646938294e+66</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.134784232521902e+21</v>
+        <v>1.21947910978639e+20</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.38198990626604e+65</v>
+        <v>-6.776205841283918e+63</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.495161100651724e+66</v>
+        <v>2.27997938526686e+68</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-138198990626603979952732278994929978618219867461409497400379179008.00 - 149494945683224379630480352097171917509000884204767141249572472356864.00</t>
+          <t>-6776205841283918040930565742608923878207205803425873602768011264.00 - 22800933935057082484170380837791504976028090080997911066558560276054016.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-8.04719587842503e+49</v>
+        <v>-7.325073389866275e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.443602765342601e+49</v>
+        <v>5.213482781885416e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274032.6002263779</v>
+        <v>269843.0847681512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202725.1043722281</v>
+        <v>200915.8230924542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78710</v>
+        <v>150440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250857.9572858929</v>
+        <v>246589.0679663418</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11392.76 - 3903597.53</t>
+          <t>6260.50 - 3932615.73</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53818.21931361489</v>
+        <v>53957.25023020255</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>725796.6869795643</v>
+        <v>718984.1171674768</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5369.490147978822</v>
+        <v>5305.645730695417</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4031.69778260121</v>
+        <v>4067.838254280636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2780</v>
+        <v>1720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4576.837350585626</v>
+        <v>4392.121046763392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>216.12 - 64489.91</t>
+          <t>229.63 - 55836.69</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1220.758884307827</v>
+        <v>1180.618334160583</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13857.29890177667</v>
+        <v>13453.69880027313</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.38418756549958</v>
+        <v>37.11962115153933</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.98114999057544</v>
+        <v>21.37353895966513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50.44732695158963</v>
+        <v>54.28945769653566</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.42 - 1378.20</t>
+          <t>0.53 - 1862.31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.768040465656767</v>
+        <v>3.827720738259254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>120.3980130123977</v>
+        <v>120.9042479385507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.280100646938294e+66</v>
+        <v>7.663576137121027e+64</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.21947910978639e+20</v>
+        <v>-9.284299759452017e+19</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-6.776205841283918e+63</v>
+        <v>-4.59850740998172e+66</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.27997938526686e+68</v>
+        <v>7.677555366340375e+66</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-6776205841283918040930565742608923878207205803425873602768011264.00 - 22800933935057082484170380837791504976028090080997911066558560276054016.00</t>
+          <t>-4598507409981720253278370495803566252984658249177017469097251700736.00 - 767772193116502054745734557459287594471029529194544971896509467459584.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-7.325073389866275e+49</v>
+        <v>-9.979626328730883e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.213482781885416e+49</v>
+        <v>6.483122241931475e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269843.0847681512</v>
+        <v>266388.3366610684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200915.8230924542</v>
+        <v>198681.8064386019</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150440</v>
+        <v>98720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246589.0679663418</v>
+        <v>240007.379134572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6260.50 - 3932615.73</t>
+          <t>10995.75 - 3242202.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53957.25023020255</v>
+        <v>53659.14236376868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>718984.1171674768</v>
+        <v>696416.5529694069</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5305.645730695417</v>
+        <v>5287.333059144792</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4067.838254280636</v>
+        <v>4070.897466438873</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1720</v>
+        <v>1930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4392.121046763392</v>
+        <v>4373.841374085411</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>229.63 - 55836.69</t>
+          <t>277.57 - 50218.50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1180.618334160583</v>
+        <v>1154.295444004228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13453.69880027313</v>
+        <v>13581.85902930043</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.11962115153933</v>
+        <v>36.75208773787025</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.37353895966513</v>
+        <v>21.35734437547204</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54.28945769653566</v>
+        <v>50.07382452534124</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.53 - 1862.31</t>
+          <t>0.22 - 957.24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.827720738259254</v>
+        <v>3.945522072331813</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>120.9042479385507</v>
+        <v>119.9079670260709</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.663576137121027e+64</v>
+        <v>4.182573611178391e+63</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-9.284299759452017e+19</v>
+        <v>6.969478585560396e+21</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.59850740998172e+66</v>
+        <v>-6.496222701237613e+66</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.677555366340375e+66</v>
+        <v>4.866601017613105e+65</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-4598507409981720253278370495803566252984658249177017469097251700736.00 - 767772193116502054745734557459287594471029529194544971896509467459584.00</t>
+          <t>-6496222701237613448804693713696920442219348689357478290201918832640.00 - 48229318348536936059717357616296176054682475955515970643897735970816.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.979626328730883e+49</v>
+        <v>-1.410606209341649e+50</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.483122241931475e+49</v>
+        <v>2.017823969091567e+50</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>266388.3366610684</v>
+        <v>271454.2230180964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>198681.8064386019</v>
+        <v>200726.3981196035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98720</v>
+        <v>76250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>240007.379134572</v>
+        <v>243088.7467382614</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10995.75 - 3242202.25</t>
+          <t>10531.39 - 3768352.13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53659.14236376868</v>
+        <v>56017.29106921107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>696416.5529694069</v>
+        <v>725728.1430046094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5287.333059144792</v>
+        <v>5320.085651916726</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4070.897466438873</v>
+        <v>4032.891234488266</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1930</v>
+        <v>2780</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4373.841374085411</v>
+        <v>4504.785888106082</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>277.57 - 50218.50</t>
+          <t>338.99 - 54837.96</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1154.295444004228</v>
+        <v>1193.464777792291</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13581.85902930043</v>
+        <v>13707.53904216058</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36.75208773787025</v>
+        <v>37.41572594802145</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.35734437547204</v>
+        <v>21.67589062453168</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50.07382452534124</v>
+        <v>55.52055719614273</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.22 - 957.24</t>
+          <t>0.23 - 1577.15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.945522072331813</v>
+        <v>3.875660934293019</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119.9079670260709</v>
+        <v>116.128798682402</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.182573611178391e+63</v>
+        <v>6.877654890576859e+64</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.969478585560396e+21</v>
+        <v>2.031877242941052e+21</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-6.496222701237613e+66</v>
+        <v>-2.028197152643725e+66</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.866601017613105e+65</v>
+        <v>6.693125704144167e+66</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-6496222701237613448804693713696920442219348689357478290201918832640.00 - 48229318348536936059717357616296176054682475955515970643897735970816.00</t>
+          <t>-2028197152643724502412939876452786067633586650828458312422786072576.00 - 669164933324491343870504604671830521231860789705886613727849601826816.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.410606209341649e+50</v>
+        <v>-8.098782726047548e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.017823969091567e+50</v>
+        <v>9.188683442114554e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>271454.2230180964</v>
+        <v>268178.920461966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200726.3981196035</v>
+        <v>200266.2345253136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76250</v>
+        <v>45360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243088.7467382614</v>
+        <v>242032.9253608087</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10531.39 - 3768352.13</t>
+          <t>9040.92 - 3496713.58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56017.29106921107</v>
+        <v>54704.62595606098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>725728.1430046094</v>
+        <v>704775.1164588442</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5320.085651916726</v>
+        <v>5364.965575846668</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4032.891234488266</v>
+        <v>4086.881292518497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2780</v>
+        <v>1790</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4504.785888106082</v>
+        <v>4540.498487863332</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>338.99 - 54837.96</t>
+          <t>308.65 - 66219.21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1193.464777792291</v>
+        <v>1198.519533950122</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13707.53904216058</v>
+        <v>13695.77862617293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.41572594802145</v>
+        <v>37.04832182616708</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.67589062453168</v>
+        <v>21.26594576954287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55.52055719614273</v>
+        <v>51.56187662914727</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.23 - 1577.15</t>
+          <t>0.43 - 888.97</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.875660934293019</v>
+        <v>3.793384179857716</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116.128798682402</v>
+        <v>119.6935713845027</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.877654890576859e+64</v>
+        <v>2.549676500909602e+65</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.031877242941052e+21</v>
+        <v>-4.583145029180087e+19</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.028197152643725e+66</v>
+        <v>-5.638377378184693e+65</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6.693125704144167e+66</v>
+        <v>2.550148753014753e+67</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-2028197152643724502412939876452786067633586650828458312422786072576.00 - 669164933324491343870504604671830521231860789705886613727849601826816.00</t>
+          <t>-563837737818469294082907817568861560728531421177039831163572584448.00 - 2550276147617743292762041891826216042895739114256939652022959026995200.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-8.098782726047548e+49</v>
+        <v>-9.27406022044901e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.188683442114554e+49</v>
+        <v>7.311593786727391e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268178.920461966</v>
+        <v>271168.7020647229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200266.2345253136</v>
+        <v>195401.9149626659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45360</v>
+        <v>63550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>242032.9253608087</v>
+        <v>254679.1486585169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9040.92 - 3496713.58</t>
+          <t>11778.38 - 3091509.05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54704.62595606098</v>
+        <v>55522.46979988659</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>704775.1164588442</v>
+        <v>716174.9044432975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5364.965575846668</v>
+        <v>5391.676498030361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4086.881292518497</v>
+        <v>4083.809647993917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1790</v>
+        <v>2240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4540.498487863332</v>
+        <v>4568.87620754716</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>308.65 - 66219.21</t>
+          <t>275.21 - 61357.91</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1198.519533950122</v>
+        <v>1221.386375396471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13695.77862617293</v>
+        <v>13878.99462539562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.04832182616708</v>
+        <v>36.26939056366829</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.26594576954287</v>
+        <v>20.96772524883068</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51.56187662914727</v>
+        <v>52.54442887383705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.43 - 888.97</t>
+          <t>0.23 - 1342.46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.793384179857716</v>
+        <v>3.828071601567344</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119.6935713845027</v>
+        <v>114.9342826135668</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.549676500909602e+65</v>
+        <v>3.112474111106019e+61</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-4.583145029180087e+19</v>
+        <v>1.458858406846595e+19</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-5.638377378184693e+65</v>
+        <v>-4.41589228743377e+65</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.550148753014753e+67</v>
+        <v>7.323764552580509e+63</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-563837737818469294082907817568861560728531421177039831163572584448.00 - 2550276147617743292762041891826216042895739114256939652022959026995200.00</t>
+          <t>-441589228743376982752553329213126160597945374270728844361735340032.00 - 442251725890997178863047804294818554822413122366977640291849207808.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.27406022044901e+49</v>
+        <v>-1.49949407665536e+50</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.311593786727391e+49</v>
+        <v>1.271361945033509e+50</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>271168.7020647229</v>
+        <v>266393.1508714281</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>195401.9149626659</v>
+        <v>197036.0100446833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63550</v>
+        <v>156680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>254679.1486585169</v>
+        <v>244623.4644868312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11778.38 - 3091509.05</t>
+          <t>14300.05 - 3630860.39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55522.46979988659</v>
+        <v>55532.72235510084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>716174.9044432975</v>
+        <v>705878.8631356093</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5391.676498030361</v>
+        <v>5416.319189061277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4083.809647993917</v>
+        <v>4083.743937825332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4568.87620754716</v>
+        <v>4660.439116581631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>275.21 - 61357.91</t>
+          <t>186.69 - 60286.29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1221.386375396471</v>
+        <v>1211.182594004628</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13878.99462539562</v>
+        <v>13851.4968285122</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36.26939056366829</v>
+        <v>36.38175973796502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20.96772524883068</v>
+        <v>21.26911336425782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52.54442887383705</v>
+        <v>49.94746194256088</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.23 - 1342.46</t>
+          <t>0.36 - 1677.03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.828071601567344</v>
+        <v>3.844879507075059</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>114.9342826135668</v>
+        <v>118.5539591681952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.112474111106019e+61</v>
+        <v>-2.547112079569112e+66</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.458858406846595e+19</v>
+        <v>-20294742447321.7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.41589228743377e+65</v>
+        <v>-2.414328715590312e+70</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.323764552580509e+63</v>
+        <v>2.416288784718192e+68</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-441589228743376982752553329213126160597945374270728844361735340032.00 - 442251725890997178863047804294818554822413122366977640291849207808.00</t>
+          <t>-24143287155903117128744563946516398363868943296195368523502341167513600.00 - 361516134561437662570709087086472070418122494708729272263134674944.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.49949407665536e+50</v>
+        <v>-1.097327797472619e+50</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.271361945033509e+50</v>
+        <v>4.610309473220741e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>266393.1508714281</v>
+        <v>267766.0327139537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>197036.0100446833</v>
+        <v>195623.4759238085</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>156680</v>
+        <v>100950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244623.4644868312</v>
+        <v>245651.5678063527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14300.05 - 3630860.39</t>
+          <t>9234.28 - 4698720.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55532.72235510084</v>
+        <v>55569.40624003088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>705878.8631356093</v>
+        <v>711069.8545395037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5416.319189061277</v>
+        <v>5360.440638642717</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4083.743937825332</v>
+        <v>4087.490075091968</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2250</v>
+        <v>2120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4660.439116581631</v>
+        <v>4507.457011390668</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>186.69 - 60286.29</t>
+          <t>200.52 - 64262.69</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1211.182594004628</v>
+        <v>1194.350566374931</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13851.4968285122</v>
+        <v>13805.5740573049</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36.38175973796502</v>
+        <v>36.17785145173608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.26911336425782</v>
+        <v>21.38544132353632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49.94746194256088</v>
+        <v>49.85653875638104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.36 - 1677.03</t>
+          <t>0.39 - 1122.39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.844879507075059</v>
+        <v>3.822008523730295</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>118.5539591681952</v>
+        <v>114.6039582326478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.547112079569112e+66</v>
+        <v>3.639149717296526e+64</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-20294742447321.7</v>
+        <v>8.407659213832897e+20</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.414328715590312e+70</v>
+        <v>-7.932261775455884e+65</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.416288784718192e+68</v>
+        <v>3.502095538372638e+66</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-24143287155903117128744563946516398363868943296195368523502341167513600.00 - 361516134561437662570709087086472070418122494708729272263134674944.00</t>
+          <t>-793226177545588365698526669610962118844876245060638468163292364800.00 - 350108618544854859930370188793348858252507177939944338066257710415872.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.097327797472619e+50</v>
+        <v>-3.325850820995773e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.610309473220741e+49</v>
+        <v>4.580890811007675e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>267766.0327139537</v>
+        <v>264961.5302049543</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>195623.4759238085</v>
+        <v>193972.0777070085</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100950</v>
+        <v>71510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>245651.5678063527</v>
+        <v>239783.1470567574</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9234.28 - 4698720.60</t>
+          <t>9793.61 - 3703457.63</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55569.40624003088</v>
+        <v>54395.54705572395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>711069.8545395037</v>
+        <v>697364.9760757985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5360.440638642717</v>
+        <v>5277.263297458623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4087.490075091968</v>
+        <v>4055.293527363071</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2120</v>
+        <v>1950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4507.457011390668</v>
+        <v>4444.338999370555</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200.52 - 64262.69</t>
+          <t>227.86 - 55164.07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1194.350566374931</v>
+        <v>1211.526225077761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13805.5740573049</v>
+        <v>13248.69220776955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36.17785145173608</v>
+        <v>37.86705592538679</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.38544132353632</v>
+        <v>21.45645625040541</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49.85653875638104</v>
+        <v>54.83415114471669</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.39 - 1122.39</t>
+          <t>0.21 - 1528.83</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.822008523730295</v>
+        <v>3.930363043220719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>114.6039582326478</v>
+        <v>125.7986881372444</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.639149717296526e+64</v>
+        <v>2.03124429424217e+67</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.407659213832897e+20</v>
+        <v>8.367013354676693e+19</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-7.932261775455884e+65</v>
+        <v>-4.558483893154849e+69</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.502095538372638e+66</v>
+        <v>2.07747657320698e+69</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-793226177545588365698526669610962118844876245060638468163292364800.00 - 350108618544854859930370188793348858252507177939944338066257710415872.00</t>
+          <t>-4558483893154849019257426702078156155816458462799584439766506172055552.00 - 207707570213227142701951747078954084564125740571166575167915692163858432.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.325850820995773e+49</v>
+        <v>-6.77009618770385e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.580890811007675e+49</v>
+        <v>7.369521824857109e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>264961.5302049543</v>
+        <v>271218.0172837084</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>193972.0777070085</v>
+        <v>200663.1582474602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71510</v>
+        <v>190130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>239783.1470567574</v>
+        <v>244006.7494345245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9793.61 - 3703457.63</t>
+          <t>6050.83 - 3221195.64</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54395.54705572395</v>
+        <v>55074.32256697872</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>697364.9760757985</v>
+        <v>727127.3054584733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5277.263297458623</v>
+        <v>5420.353266690646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4055.293527363071</v>
+        <v>4116.743728373704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1950</v>
+        <v>2910</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4444.338999370555</v>
+        <v>4636.431134549382</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>227.86 - 55164.07</t>
+          <t>297.52 - 58625.05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1211.526225077761</v>
+        <v>1197.964834734108</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13248.69220776955</v>
+        <v>14011.48161686066</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.86705592538679</v>
+        <v>36.94193215931571</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.45645625040541</v>
+        <v>21.07149358262323</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54.83415114471669</v>
+        <v>52.30665119433915</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.21 - 1528.83</t>
+          <t>0.32 - 1296.47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.930363043220719</v>
+        <v>3.81449420606826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>125.7986881372444</v>
+        <v>119.2113070998866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.03124429424217e+67</v>
+        <v>-4.156410276039387e+62</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.367013354676693e+19</v>
+        <v>2.179917338045568e+19</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.558483893154849e+69</v>
+        <v>-3.260250812209071e+66</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.07747657320698e+69</v>
+        <v>3.355124560898336e+64</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-4558483893154849019257426702078156155816458462799584439766506172055552.00 - 207707570213227142701951747078954084564125740571166575167915692163858432.00</t>
+          <t>-3260250812209070984698902239819761902096115919024207383802819903488.00 - 24225187530301966819132441823675810425099509806377314407774420992.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-6.77009618770385e+49</v>
+        <v>-4.745358392292771e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.369521824857109e+49</v>
+        <v>7.826951552873866e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>271218.0172837084</v>
+        <v>264895.0899223682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200663.1582474602</v>
+        <v>195419.0426252054</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190130</v>
+        <v>205790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244006.7494345245</v>
+        <v>240290.6879913874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6050.83 - 3221195.64</t>
+          <t>12266.89 - 3245691.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55074.32256697872</v>
+        <v>53291.49796046772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>727127.3054584733</v>
+        <v>722038.2706785639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5420.353266690646</v>
+        <v>5397.244534016268</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4116.743728373704</v>
+        <v>4106.831843116734</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2910</v>
+        <v>1870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4636.431134549382</v>
+        <v>4650.845716404599</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>297.52 - 58625.05</t>
+          <t>162.22 - 89765.52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1197.964834734108</v>
+        <v>1244.780832154289</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14011.48161686066</v>
+        <v>13862.42696747053</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36.94193215931571</v>
+        <v>37.01012466325379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.07149358262323</v>
+        <v>21.25743356775344</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52.30665119433915</v>
+        <v>53.45585099476454</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.32 - 1296.47</t>
+          <t>0.36 - 2085.63</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.81449420606826</v>
+        <v>3.884688942506262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119.2113070998866</v>
+        <v>119.6000487230888</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-4.156410276039387e+62</v>
+        <v>6.064788081498626e+62</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.179917338045568e+19</v>
+        <v>-833249275975265.2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-3.260250812209071e+66</v>
+        <v>-1.166232486207181e+67</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.355124560898336e+64</v>
+        <v>1.74356881186619e+65</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-3260250812209070984698902239819761902096115919024207383802819903488.00 - 24225187530301966819132441823675810425099509806377314407774420992.00</t>
+          <t>-11662324862071810437754712274472224714324110332722214922559588139008.00 - 12374597082525386990105752510719902463063735496177728615938078539776.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.745358392292771e+49</v>
+        <v>-7.79550166779982e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.826951552873866e+49</v>
+        <v>1.299445118773556e+50</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_estadistica_descriptiva.xlsx
+++ b/data_cripto/montecarlo_estadistica_descriptiva.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>264895.0899223682</v>
+        <v>270042.9922231523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>195419.0426252054</v>
+        <v>200543.8713035783</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205790</v>
+        <v>93340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>240290.6879913874</v>
+        <v>242541.9363110275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12266.89 - 3245691.42</t>
+          <t>5693.54 - 5122883.61</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53291.49796046772</v>
+        <v>55804.45879228471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>722038.2706785639</v>
+        <v>713733.8359992212</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5397.244534016268</v>
+        <v>5319.325621616483</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4106.831843116734</v>
+        <v>4063.748354269825</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1870</v>
+        <v>1760</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4650.845716404599</v>
+        <v>4439.316546900154</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>162.22 - 89765.52</t>
+          <t>234.03 - 54914.18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1244.780832154289</v>
+        <v>1206.150853621813</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13862.42696747053</v>
+        <v>13748.06487493658</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37.01012466325379</v>
+        <v>35.79888403457077</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.25743356775344</v>
+        <v>21.00131540394275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53.45585099476454</v>
+        <v>50.54785011964768</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.36 - 2085.63</t>
+          <t>0.48 - 1087.87</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.884688942506262</v>
+        <v>3.641780205553256</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>119.6000487230888</v>
+        <v>115.1683034734612</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.064788081498626e+62</v>
+        <v>3.29062168056999e+67</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-833249275975265.2</v>
+        <v>8.641771953440037e+20</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.166232486207181e+67</v>
+        <v>-1.253930288348395e+64</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.74356881186619e+65</v>
+        <v>3.287028803871715e+69</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-11662324862071810437754712274472224714324110332722214922559588139008.00 - 12374597082525386990105752510719902463063735496177728615938078539776.00</t>
+          <t>-12539302883483952322352125397981747929116172725182355548619669504.00 - 328719172107940679827640419631476501825827860482693591774398484764950528.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-7.79550166779982e+49</v>
+        <v>-7.555491009525916e+49</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.299445118773556e+50</v>
+        <v>8.548346917843058e+49</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
